--- a/output/pdf_financials_xlsx/ASE.xlsx
+++ b/output/pdf_financials_xlsx/ASE.xlsx
@@ -1153,31 +1153,31 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>1.241156</v>
+        <v>-1.241156</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1.19343</v>
+        <v>-1.19343</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.790218</v>
+        <v>-0.790218</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.71147</v>
+        <v>-0.71147</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.852863</v>
+        <v>-0.852863</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.896127</v>
+        <v>-0.896127</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.665892</v>
+        <v>-0.665892</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.58972</v>
+        <v>-0.58972</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.501401</v>
+        <v>-0.501401</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>-0.673168</v>
@@ -1405,31 +1405,31 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>1.241156</v>
+        <v>-1.241156</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1.19343</v>
+        <v>-1.19343</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.790218</v>
+        <v>-0.790218</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.71147</v>
+        <v>-0.71147</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.852863</v>
+        <v>-0.852863</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.896127</v>
+        <v>-0.896127</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0.665892</v>
+        <v>-0.665892</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.58972</v>
+        <v>-0.58972</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.501401</v>
+        <v>-0.501401</v>
       </c>
       <c r="K20" s="3" t="n">
         <v>-0.673168</v>
@@ -1552,31 +1552,31 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>1.241156</v>
+        <v>-1.241156</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>1.19343</v>
+        <v>-1.19343</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.790218</v>
+        <v>-0.790218</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.71147</v>
+        <v>-0.71147</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.852863</v>
+        <v>-0.852863</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.896127</v>
+        <v>-0.896127</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0.665892</v>
+        <v>-0.665892</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>0.58972</v>
+        <v>-0.58972</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.501401</v>
+        <v>-0.501401</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>-0.673168</v>
@@ -1703,22 +1703,22 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>12.41156</v>
+        <v>-12.41156</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>19.8905</v>
+        <v>-19.8905</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>19.75545</v>
+        <v>-19.75545</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>23.715667</v>
+        <v>-23.715667</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>21.321575</v>
+        <v>-21.321575</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>44.80635</v>
+        <v>-44.80635</v>
       </c>
       <c r="H26" s="1" t="inlineStr">
         <is>
@@ -1760,31 +1760,31 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>1.241156</v>
+        <v>-1.241156</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>1.19343</v>
+        <v>-1.19343</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.790218</v>
+        <v>-0.790218</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0.71147</v>
+        <v>-0.71147</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.852863</v>
+        <v>-0.852863</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.896127</v>
+        <v>-0.896127</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.665892</v>
+        <v>-0.665892</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.58972</v>
+        <v>-0.58972</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.501401</v>
+        <v>-0.501401</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>-0.673168</v>
@@ -1858,31 +1858,31 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>1.241156</v>
+        <v>-1.241156</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>1.19343</v>
+        <v>-1.19343</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.790218</v>
+        <v>-0.790218</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.71147</v>
+        <v>-0.71147</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.852863</v>
+        <v>-0.852863</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.896127</v>
+        <v>-0.896127</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.665892</v>
+        <v>-0.665892</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.58972</v>
+        <v>-0.58972</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.501401</v>
+        <v>-0.501401</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>-0.673168</v>
@@ -1982,31 +1982,31 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K31" s="3" t="n">
         <v>-0</v>
@@ -4975,10 +4975,10 @@
         <v>0</v>
       </c>
       <c r="C91" s="3" t="n">
-        <v>0</v>
+        <v>-2.6e-05</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0</v>
+        <v>0.25752</v>
       </c>
       <c r="E91" s="3" t="n">
         <v>0.25752</v>
@@ -5024,43 +5024,43 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.078878</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.078878</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.078878</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.078878</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.111378</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.159856</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.159856</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.159856</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.30268</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>0.417286</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>0.282</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>5.381</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>5.381</v>
       </c>
     </row>
     <row r="93">
@@ -10006,7 +10006,11 @@
           <t>Reserve for warrants 15,016</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
           <t>-</t>
@@ -13262,7 +13266,11 @@
           <t>Reserve for warrants</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E70" t="inlineStr">
         <is>
           <t>-</t>
@@ -21632,7 +21640,11 @@
           <t>Reserve for warrants (Note 13)</t>
         </is>
       </c>
-      <c r="D167" t="inlineStr"/>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E167" t="inlineStr">
         <is>
           <t>-</t>
@@ -25292,7 +25304,11 @@
           <t>Reserve for warrants (Note 6) 177,965</t>
         </is>
       </c>
-      <c r="D210" t="inlineStr"/>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E210" t="inlineStr">
         <is>
           <t>-</t>
@@ -26540,7 +26556,11 @@
           <t>Reserve for warrants (Note 7)</t>
         </is>
       </c>
-      <c r="D225" t="inlineStr"/>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E225" t="inlineStr">
         <is>
           <t>-</t>
@@ -29106,7 +29126,11 @@
           <t>Reserve for warrants (Note 7) 159,856</t>
         </is>
       </c>
-      <c r="D255" t="inlineStr"/>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E255" t="inlineStr">
         <is>
           <t>-</t>
@@ -32164,7 +32188,11 @@
           <t>Reserve for warrants (Note 7) 123,775</t>
         </is>
       </c>
-      <c r="D290" t="inlineStr"/>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E290" t="inlineStr">
         <is>
           <t>-</t>
@@ -33742,7 +33770,11 @@
           <t>Reserve for warrants (Note 7) 111,378</t>
         </is>
       </c>
-      <c r="D308" t="inlineStr"/>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E308" t="inlineStr">
         <is>
           <t>-</t>
@@ -35926,7 +35958,11 @@
           <t>Reserve for warrants (Note 7) 78,878</t>
         </is>
       </c>
-      <c r="D333" t="inlineStr"/>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E333" t="inlineStr">
         <is>
           <t>-</t>
@@ -36604,7 +36640,11 @@
           <t>Cumulative translation reserve</t>
         </is>
       </c>
-      <c r="D341" t="inlineStr"/>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E341" t="inlineStr">
         <is>
           <t>-</t>
@@ -37908,7 +37948,11 @@
           <t>Cumulative translation reserve</t>
         </is>
       </c>
-      <c r="D356" t="inlineStr"/>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E356" t="inlineStr">
         <is>
           <t>-</t>
@@ -77087,28 +77131,28 @@
         </is>
       </c>
       <c r="F816" s="5" t="n">
-        <v>1.19343</v>
+        <v>-1.19343</v>
       </c>
       <c r="G816" s="5" t="n">
-        <v>0.790218</v>
+        <v>-0.790218</v>
       </c>
       <c r="H816" s="5" t="n">
-        <v>0.71147</v>
+        <v>-0.71147</v>
       </c>
       <c r="I816" s="5" t="n">
-        <v>0.852863</v>
+        <v>-0.852863</v>
       </c>
       <c r="J816" s="5" t="n">
-        <v>0.896127</v>
+        <v>-0.896127</v>
       </c>
       <c r="K816" s="5" t="n">
-        <v>0.665892</v>
+        <v>-0.665892</v>
       </c>
       <c r="L816" s="5" t="n">
-        <v>0.58972</v>
+        <v>-0.58972</v>
       </c>
       <c r="M816" s="5" t="n">
-        <v>0.501401</v>
+        <v>-0.501401</v>
       </c>
       <c r="N816" t="inlineStr">
         <is>
@@ -77266,13 +77310,13 @@
         </is>
       </c>
       <c r="K818" s="5" t="n">
-        <v>0.899672</v>
+        <v>-0.899672</v>
       </c>
       <c r="L818" s="5" t="n">
-        <v>0.304435</v>
+        <v>-0.304435</v>
       </c>
       <c r="M818" s="5" t="n">
-        <v>0.472705</v>
+        <v>-0.472705</v>
       </c>
       <c r="N818" t="inlineStr">
         <is>
@@ -78817,16 +78861,16 @@
         </is>
       </c>
       <c r="F837" s="5" t="n">
-        <v>1.193456</v>
+        <v>-1.193456</v>
       </c>
       <c r="G837" s="5" t="n">
-        <v>0.532672</v>
+        <v>-0.532672</v>
       </c>
       <c r="H837" s="5" t="n">
-        <v>0.392958</v>
+        <v>-0.392958</v>
       </c>
       <c r="I837" s="5" t="n">
-        <v>0.574343</v>
+        <v>-0.574343</v>
       </c>
       <c r="J837" t="inlineStr">
         <is>
@@ -79152,16 +79196,16 @@
         </is>
       </c>
       <c r="E841" s="5" t="n">
-        <v>1.241156</v>
+        <v>-1.241156</v>
       </c>
       <c r="F841" s="5" t="n">
-        <v>1.19343</v>
+        <v>-1.19343</v>
       </c>
       <c r="G841" s="5" t="n">
-        <v>0.790218</v>
+        <v>-0.790218</v>
       </c>
       <c r="H841" s="5" t="n">
-        <v>0.71147</v>
+        <v>-0.71147</v>
       </c>
       <c r="I841" t="inlineStr">
         <is>
@@ -79844,10 +79888,10 @@
         </is>
       </c>
       <c r="E849" s="5" t="n">
-        <v>1.241156</v>
+        <v>-1.241156</v>
       </c>
       <c r="F849" s="5" t="n">
-        <v>1.193456</v>
+        <v>-1.193456</v>
       </c>
       <c r="G849" t="inlineStr">
         <is>
@@ -80626,7 +80670,7 @@
         </is>
       </c>
       <c r="E858" s="5" t="n">
-        <v>1.241156</v>
+        <v>-1.241156</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -80802,7 +80846,7 @@
         </is>
       </c>
       <c r="E860" s="5" t="n">
-        <v>1.241156</v>
+        <v>-1.241156</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/ASE.xlsx
+++ b/output/pdf_financials_xlsx/ASE.xlsx
@@ -2113,46 +2113,46 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.756374</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.02855</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.014058</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.014058</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.021449</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.004982</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.014334</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.00557</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.00557</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.479098</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>5.849</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>2.106</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>1.553</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>25.953</v>
       </c>
     </row>
     <row r="35">
@@ -2211,46 +2211,46 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.756374</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.046</v>
+        <v>0.07455000000000001</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.014058</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.014058</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.021449</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.004982</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.014334</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.00557</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.00557</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.479098</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>7.509</v>
+        <v>13.358</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>4.654</v>
+        <v>6.76</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>2.429</v>
+        <v>3.982</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>1.43</v>
+        <v>27.383</v>
       </c>
     </row>
     <row r="37">
@@ -2799,46 +2799,46 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.843546</v>
+        <v>0.087172</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.117725</v>
+        <v>0.089175</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.027023</v>
+        <v>0.012965</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.027023</v>
+        <v>0.012965</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.031499</v>
+        <v>0.01005</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.024742</v>
+        <v>0.01976</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.040737</v>
+        <v>0.026403</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.01557</v>
+        <v>0.01</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.01557</v>
+        <v>0.01</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.523152</v>
+        <v>0.044054</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>11.535355</v>
+        <v>5.686355</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>34.689</v>
+        <v>32.583</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>32.227</v>
+        <v>30.674</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>43.791</v>
+        <v>17.838</v>
       </c>
     </row>
     <row r="49">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -10802,7 +10802,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -19230,7 +19230,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -23884,7 +23884,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -25822,7 +25822,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -27802,7 +27802,7 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -30856,7 +30856,7 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
@@ -32620,7 +32620,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
@@ -34546,7 +34546,7 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
@@ -36810,7 +36810,7 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E343" s="5" t="n">
@@ -38390,7 +38390,7 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E361" s="5" t="n">

--- a/output/pdf_financials_xlsx/ASE.xlsx
+++ b/output/pdf_financials_xlsx/ASE.xlsx
@@ -710,31 +710,31 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.382561</v>
+        <v>0.394561</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.561793</v>
+        <v>0.6130910000000001</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.447224</v>
+        <v>0.488362</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.326091</v>
+        <v>0.369709</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.404254</v>
+        <v>0.451072</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.698493</v>
+        <v>0.75057</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.48565</v>
+        <v>0.541312</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.223429</v>
+        <v>0.268284</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.202447</v>
+        <v>0.257647</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>0.353481</v>
@@ -857,31 +857,31 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.382561</v>
+        <v>0.394561</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.561793</v>
+        <v>0.6130910000000001</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.447224</v>
+        <v>0.488362</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.326091</v>
+        <v>0.369709</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.404254</v>
+        <v>0.451072</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.698493</v>
+        <v>0.75057</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.48565</v>
+        <v>0.541312</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.223429</v>
+        <v>0.268284</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.202447</v>
+        <v>0.257647</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>0.673168</v>
@@ -906,31 +906,31 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.382561</v>
+        <v>-0.394561</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.561793</v>
+        <v>-0.6130910000000001</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.447224</v>
+        <v>-0.488362</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-0.326091</v>
+        <v>-0.369709</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-0.404254</v>
+        <v>-0.451072</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>-0.698493</v>
+        <v>-0.75057</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>-0.48565</v>
+        <v>-0.541312</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>-0.223429</v>
+        <v>-0.268284</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0.202447</v>
+        <v>-0.257647</v>
       </c>
       <c r="K11" s="1" t="inlineStr">
         <is>
@@ -1189,10 +1189,10 @@
         <v>-200.524</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>-103.201</v>
+        <v>-39.972</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>-78.509</v>
+        <v>-81.502</v>
       </c>
     </row>
     <row r="17">
@@ -1238,10 +1238,10 @@
         <v>12.01</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>-0</v>
+        <v>-63.229</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>-0</v>
+        <v>2.993</v>
       </c>
     </row>
     <row r="18">
@@ -1796,10 +1796,10 @@
         <v>-200.524</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-103.201</v>
+        <v>-39.972</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-78.509</v>
+        <v>-81.502</v>
       </c>
     </row>
     <row r="28">
@@ -1894,10 +1894,10 @@
         <v>-200.524</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-103.201</v>
+        <v>-39.972</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-78.509</v>
+        <v>-81.502</v>
       </c>
     </row>
     <row r="30">
@@ -2018,10 +2018,10 @@
         <v>-5.989308013005925</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>-0</v>
+        <v>-158.1832282597818</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>-0</v>
+        <v>-3.672302520183554</v>
       </c>
     </row>
     <row r="32">
@@ -3788,16 +3788,16 @@
         <v>0</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>1.503</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>154.609</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>136.412</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>70.52800000000001</v>
       </c>
     </row>
     <row r="68">
@@ -3837,16 +3837,16 @@
         <v>0.339306</v>
       </c>
       <c r="L68" s="3" t="n">
-        <v>11.948</v>
+        <v>13.451</v>
       </c>
       <c r="M68" s="3" t="n">
-        <v>245.243</v>
+        <v>399.852</v>
       </c>
       <c r="N68" s="3" t="n">
-        <v>304.69</v>
+        <v>441.102</v>
       </c>
       <c r="O68" s="3" t="n">
-        <v>293.628</v>
+        <v>364.156</v>
       </c>
     </row>
     <row r="69">
@@ -5894,13 +5894,13 @@
         <v>0</v>
       </c>
       <c r="M110" s="3" t="n">
-        <v>0</v>
+        <v>7.26</v>
       </c>
       <c r="N110" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O110" s="3" t="n">
-        <v>0</v>
+        <v>3.808</v>
       </c>
     </row>
     <row r="111">
@@ -6914,12 +6914,10 @@
         <v>0.02855</v>
       </c>
       <c r="E130" s="3" t="n">
-        <v>0.021801</v>
-      </c>
-      <c r="F130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.014058</v>
+      </c>
+      <c r="F130" s="3" t="n">
+        <v>0.021449</v>
       </c>
       <c r="G130" s="3" t="n">
         <v>0.004982</v>
@@ -6927,20 +6925,14 @@
       <c r="H130" s="3" t="n">
         <v>0.032486</v>
       </c>
-      <c r="I130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I130" s="3" t="n">
+        <v>0.014334</v>
+      </c>
+      <c r="J130" s="3" t="n">
+        <v>0.00557</v>
+      </c>
+      <c r="K130" s="3" t="n">
+        <v>0.019707</v>
       </c>
       <c r="L130" s="3" t="n">
         <v>0.479</v>
@@ -7020,10 +7012,10 @@
         <v>-0.014492</v>
       </c>
       <c r="E132" s="3" t="n">
-        <v>-0.000352</v>
+        <v>0.007391</v>
       </c>
       <c r="F132" s="3" t="n">
-        <v>-0.001728</v>
+        <v>-0.016467</v>
       </c>
       <c r="G132" s="3" t="n">
         <v>0.027504</v>
@@ -7071,10 +7063,8 @@
       <c r="E133" s="3" t="n">
         <v>0.021449</v>
       </c>
-      <c r="F133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F133" s="3" t="n">
+        <v>0.004982</v>
       </c>
       <c r="G133" s="3" t="n">
         <v>0.032486</v>
@@ -7082,20 +7072,14 @@
       <c r="H133" s="3" t="n">
         <v>0.014334</v>
       </c>
-      <c r="I133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I133" s="3" t="n">
+        <v>0.00557</v>
+      </c>
+      <c r="J133" s="3" t="n">
+        <v>0.019707</v>
+      </c>
+      <c r="K133" s="3" t="n">
+        <v>0.479098</v>
       </c>
       <c r="L133" s="3" t="n">
         <v>5.849</v>
@@ -39882,7 +39866,11 @@
           <t>Accretion 6,370</t>
         </is>
       </c>
-      <c r="D378" t="inlineStr"/>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E378" t="inlineStr">
         <is>
           <t>-</t>
@@ -41184,7 +41172,11 @@
           <t>Deferred income tax expense (recovery) 1,329</t>
         </is>
       </c>
-      <c r="D393" t="inlineStr"/>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E393" t="inlineStr">
         <is>
           <t>-</t>
@@ -46790,7 +46782,11 @@
           <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D458" t="inlineStr"/>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E458" t="inlineStr">
         <is>
           <t>-</t>
@@ -51222,7 +51218,11 @@
           <t>Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D510" t="inlineStr"/>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E510" t="inlineStr">
         <is>
           <t>-</t>
@@ -54222,7 +54222,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D545" t="inlineStr"/>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E545" t="inlineStr">
         <is>
           <t>-</t>
@@ -61052,7 +61056,11 @@
           <t>Cash at beginning of the year</t>
         </is>
       </c>
-      <c r="D625" t="inlineStr"/>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E625" t="inlineStr">
         <is>
           <t>-</t>
@@ -61122,7 +61130,11 @@
           <t>Cash at end of the year</t>
         </is>
       </c>
-      <c r="D626" t="inlineStr"/>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E626" t="inlineStr">
         <is>
           <t>-</t>
@@ -63068,7 +63080,11 @@
           <t>Share issued for cash</t>
         </is>
       </c>
-      <c r="D650" t="inlineStr"/>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E650" t="inlineStr">
         <is>
           <t>-</t>
@@ -63556,7 +63572,11 @@
           <t>Cash at end of the year $</t>
         </is>
       </c>
-      <c r="D656" t="inlineStr"/>
+      <c r="D656" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E656" t="inlineStr">
         <is>
           <t>-</t>
@@ -65988,7 +66008,11 @@
           <t>Proceeds from share issuance</t>
         </is>
       </c>
-      <c r="D685" t="inlineStr"/>
+      <c r="D685" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E685" s="5" t="n">
         <v>1.81866</v>
       </c>
@@ -70384,7 +70408,11 @@
           <t>Income tax recovery (expense) 28</t>
         </is>
       </c>
-      <c r="D736" t="inlineStr"/>
+      <c r="D736" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E736" t="inlineStr">
         <is>
           <t>-</t>
@@ -71962,7 +71990,11 @@
           <t>Income tax recovery (expense) 29</t>
         </is>
       </c>
-      <c r="D755" t="inlineStr"/>
+      <c r="D755" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E755" t="inlineStr">
         <is>
           <t>-</t>
@@ -76434,7 +76466,11 @@
           <t>Directors' fees (Note 10)</t>
         </is>
       </c>
-      <c r="D808" t="inlineStr"/>
+      <c r="D808" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E808" t="inlineStr">
         <is>
           <t>-</t>
@@ -77536,7 +77572,11 @@
           <t>Directors' fees (Note 11)</t>
         </is>
       </c>
-      <c r="D821" t="inlineStr"/>
+      <c r="D821" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E821" s="5" t="n">
         <v>0.012</v>
       </c>
@@ -80320,7 +80360,11 @@
           <t>Directors' fees (note 11)</t>
         </is>
       </c>
-      <c r="D854" t="inlineStr"/>
+      <c r="D854" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E854" s="5" t="n">
         <v>0.012</v>
       </c>
